--- a/public/DataUser/user.xlsx
+++ b/public/DataUser/user.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp_oh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wasis\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203229D1-64B6-43D7-8E66-387F050F9F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43167912-F30E-4272-B3F3-86F4C91E598D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
   <si>
     <t>user</t>
   </si>
   <si>
-    <t>user@gmail.com</t>
+    <t>rehan</t>
+  </si>
+  <si>
+    <t>rehan@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -385,18 +388,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -404,8 +407,8 @@
       <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" t="s">
-        <v>0</v>
+      <c r="E1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/public/DataUser/user.xlsx
+++ b/public/DataUser/user.xlsx
@@ -8,47 +8,93 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp_oh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF804E7C-0605-4336-A400-3AB903CDFBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D895338-C04E-4EBD-AA7C-FD8B4DCE443E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5652" yWindow="2724" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
-  <si>
-    <t>rai</t>
-  </si>
-  <si>
-    <t>rai@gmail.com</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>user</t>
   </si>
   <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>ian</t>
-  </si>
-  <si>
-    <t>ian@gmail.com</t>
+    <t>Ahmad</t>
+  </si>
+  <si>
+    <t>Budi</t>
+  </si>
+  <si>
+    <t>Citra</t>
+  </si>
+  <si>
+    <t>Dewi</t>
+  </si>
+  <si>
+    <t>Eka</t>
+  </si>
+  <si>
+    <t>Fajar</t>
+  </si>
+  <si>
+    <t>ahmad@gmail.com</t>
+  </si>
+  <si>
+    <t>budi@gmail.com</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>citra@gmail.com</t>
+  </si>
+  <si>
+    <t>dewi@gmail.com</t>
+  </si>
+  <si>
+    <t>eka@gmail.com</t>
+  </si>
+  <si>
+    <t>fajar@gmail.com</t>
+  </si>
+  <si>
+    <t>asu</t>
+  </si>
+  <si>
+    <t>aaa</t>
+  </si>
+  <si>
+    <t>bbb</t>
+  </si>
+  <si>
+    <t>ccc</t>
+  </si>
+  <si>
+    <t>ddd</t>
+  </si>
+  <si>
+    <t>eee</t>
+  </si>
+  <si>
+    <t>fff</t>
   </si>
 </sst>
 </file>
@@ -397,45 +443,127 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1">
-        <v>123</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
-        <v>123</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B26" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B1" r:id="rId1" xr:uid="{980EC06E-D34D-4605-AFAD-2BA82803A060}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{D69C84B5-9AE5-4EE0-8D15-B3C4FCD99983}"/>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{4EB052C1-D215-48C7-ADFD-5201E70536C6}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{FDC4CEC2-8907-4E5E-B899-5DE8B45A2F3C}"/>
+    <hyperlink ref="B5" r:id="rId3" xr:uid="{D56A4B1E-0E62-4B37-AF96-195D7D724F09}"/>
+    <hyperlink ref="B6" r:id="rId4" xr:uid="{82C2D395-1A2B-4D8F-9006-2C83418E756F}"/>
+    <hyperlink ref="B2" r:id="rId5" xr:uid="{D69C84B5-9AE5-4EE0-8D15-B3C4FCD99983}"/>
+    <hyperlink ref="B1" r:id="rId6" xr:uid="{980EC06E-D34D-4605-AFAD-2BA82803A060}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>